--- a/data/progbook_inputs.xlsx
+++ b/data/progbook_inputs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://burnetinstitute.sharepoint.com/sites/WG-Modelling-HCVvaccinemodel/Shared Documents/HCV vaccine model/HCV vaccine model/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farah.houdroge\Documents\GitHub\hcv-vaccine\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{5260720A-E352-4F90-B81D-5AD4DCF21178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{186AF54C-8ADF-4947-A6C1-4578C7485A31}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A436CEC3-1484-4EF8-A944-DB4460F853F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E2E90E70-2F54-4097-8786-78C8F6F97317}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E2E90E70-2F54-4097-8786-78C8F6F97317}"/>
   </bookViews>
   <sheets>
     <sheet name="interventions" sheetId="7" r:id="rId1"/>
@@ -482,7 +482,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="87">
   <si>
     <t>code</t>
   </si>
@@ -737,6 +737,12 @@
   </si>
   <si>
     <t>PWID + Campaign + Prison + Schools + Adults</t>
+  </si>
+  <si>
+    <t>Prisoners_PWID_males</t>
+  </si>
+  <si>
+    <t>Prisoners_PWID_females</t>
   </si>
 </sst>
 </file>
@@ -1000,7 +1006,17 @@
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1338,13 +1354,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7293DEF-C325-4FE3-AD5B-B41F22CF0DA3}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:B31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="80.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="80.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1352,7 +1368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>38</v>
       </c>
@@ -1360,7 +1376,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>39</v>
       </c>
@@ -1368,7 +1384,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>40</v>
       </c>
@@ -1376,7 +1392,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>37</v>
       </c>
@@ -1384,7 +1400,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>41</v>
       </c>
@@ -1392,7 +1408,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>64</v>
       </c>
@@ -1400,7 +1416,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>65</v>
       </c>
@@ -1408,7 +1424,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>63</v>
       </c>
@@ -1416,70 +1432,70 @@
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="3"/>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="3"/>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="3"/>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="3"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" s="3"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" s="3"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" s="3"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" s="3"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" s="3"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" s="3"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" s="3"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" s="3"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" s="3"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" s="3"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" s="3"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A28" s="3"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" s="4"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A30" s="4"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" s="3"/>
     </row>
   </sheetData>
@@ -1490,25 +1506,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01B95C70-A891-4037-BF3D-C1EB7C57DA84}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:M47"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O47"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.7265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.81640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.90625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="22.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1548,8 +1566,14 @@
       <c r="M1" s="10" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N1" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="str">
         <f>IF(ISBLANK(interventions!A2),"",interventions!A2)</f>
         <v>pwid_vax</v>
@@ -1571,7 +1595,7 @@
       <c r="L2" s="11"/>
       <c r="M2" s="11"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="str">
         <f>IF(ISBLANK(interventions!A3),"",interventions!A3)</f>
         <v>pwid_vax_campaign</v>
@@ -1593,7 +1617,7 @@
       <c r="L3" s="11"/>
       <c r="M3" s="11"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="str">
         <f>IF(ISBLANK(interventions!A4),"",interventions!A4)</f>
         <v>prison_vax_campaign</v>
@@ -1614,8 +1638,14 @@
       <c r="M4" s="11" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N4" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="O4" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="str">
         <f>IF(ISBLANK(interventions!A5),"",interventions!A5)</f>
         <v>teen_vax</v>
@@ -1636,8 +1666,10 @@
       <c r="K5" s="11"/>
       <c r="L5" s="11"/>
       <c r="M5" s="11"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N5" s="11"/>
+      <c r="O5" s="11"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="str">
         <f>IF(ISBLANK(interventions!A6),"",interventions!A6)</f>
         <v>adults_vax</v>
@@ -1658,8 +1690,10 @@
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
       <c r="M6" s="11"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N6" s="11"/>
+      <c r="O6" s="11"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="str">
         <f>IF(ISBLANK(interventions!A7),"",interventions!A7)</f>
         <v>pwid_counter</v>
@@ -1680,8 +1714,10 @@
       <c r="K7" s="11"/>
       <c r="L7" s="11"/>
       <c r="M7" s="11"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N7" s="11"/>
+      <c r="O7" s="11"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="str">
         <f>IF(ISBLANK(interventions!A8),"",interventions!A8)</f>
         <v>prison_counter</v>
@@ -1702,8 +1738,14 @@
       <c r="M8" s="11" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N8" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="O8" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="str">
         <f>IF(ISBLANK(interventions!A9),"",interventions!A9)</f>
         <v>status_quo</v>
@@ -1744,8 +1786,14 @@
       <c r="M9" s="11" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N9" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="O9" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="str">
         <f>IF(ISBLANK(interventions!A10),"",interventions!A10)</f>
         <v/>
@@ -1763,7 +1811,7 @@
       <c r="L10" s="11"/>
       <c r="M10" s="11"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="str">
         <f>IF(ISBLANK(interventions!A11),"",interventions!A11)</f>
         <v/>
@@ -1781,7 +1829,7 @@
       <c r="L11" s="11"/>
       <c r="M11" s="11"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="str">
         <f>IF(ISBLANK(interventions!A12),"",interventions!A12)</f>
         <v/>
@@ -1799,7 +1847,7 @@
       <c r="L12" s="11"/>
       <c r="M12" s="11"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="str">
         <f>IF(ISBLANK(interventions!A13),"",interventions!A13)</f>
         <v/>
@@ -1817,7 +1865,7 @@
       <c r="L13" s="11"/>
       <c r="M13" s="11"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="str">
         <f>IF(ISBLANK(interventions!A14),"",interventions!A14)</f>
         <v/>
@@ -1835,7 +1883,7 @@
       <c r="L14" s="11"/>
       <c r="M14" s="11"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="str">
         <f>IF(ISBLANK(interventions!A15),"",interventions!A15)</f>
         <v/>
@@ -1853,7 +1901,7 @@
       <c r="L15" s="11"/>
       <c r="M15" s="11"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="str">
         <f>IF(ISBLANK(interventions!A16),"",interventions!A16)</f>
         <v/>
@@ -1871,7 +1919,7 @@
       <c r="L16" s="11"/>
       <c r="M16" s="11"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="str">
         <f>IF(ISBLANK(interventions!A17),"",interventions!A17)</f>
         <v/>
@@ -1889,7 +1937,7 @@
       <c r="L17" s="11"/>
       <c r="M17" s="11"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="str">
         <f>IF(ISBLANK(interventions!A18),"",interventions!A18)</f>
         <v/>
@@ -1907,7 +1955,7 @@
       <c r="L18" s="11"/>
       <c r="M18" s="11"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="str">
         <f>IF(ISBLANK(interventions!A19),"",interventions!A19)</f>
         <v/>
@@ -1925,7 +1973,7 @@
       <c r="L19" s="11"/>
       <c r="M19" s="11"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="str">
         <f>IF(ISBLANK(interventions!A20),"",interventions!A20)</f>
         <v/>
@@ -1943,7 +1991,7 @@
       <c r="L20" s="11"/>
       <c r="M20" s="11"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="str">
         <f>IF(ISBLANK(interventions!A21),"",interventions!A21)</f>
         <v/>
@@ -1961,7 +2009,7 @@
       <c r="L21" s="11"/>
       <c r="M21" s="11"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="str">
         <f>IF(ISBLANK(interventions!A22),"",interventions!A22)</f>
         <v/>
@@ -1979,7 +2027,7 @@
       <c r="L22" s="11"/>
       <c r="M22" s="11"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="str">
         <f>IF(ISBLANK(interventions!A23),"",interventions!A23)</f>
         <v/>
@@ -1997,7 +2045,7 @@
       <c r="L23" s="11"/>
       <c r="M23" s="11"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="str">
         <f>IF(ISBLANK(interventions!A24),"",interventions!A24)</f>
         <v/>
@@ -2015,7 +2063,7 @@
       <c r="L24" s="11"/>
       <c r="M24" s="11"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="str">
         <f>IF(ISBLANK(interventions!A25),"",interventions!A25)</f>
         <v/>
@@ -2033,7 +2081,7 @@
       <c r="L25" s="11"/>
       <c r="M25" s="11"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="str">
         <f>IF(ISBLANK(interventions!A26),"",interventions!A26)</f>
         <v/>
@@ -2051,7 +2099,7 @@
       <c r="L26" s="11"/>
       <c r="M26" s="11"/>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="str">
         <f>IF(ISBLANK(interventions!A27),"",interventions!A27)</f>
         <v/>
@@ -2069,7 +2117,7 @@
       <c r="L27" s="11"/>
       <c r="M27" s="11"/>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="str">
         <f>IF(ISBLANK(interventions!A28),"",interventions!A28)</f>
         <v/>
@@ -2087,7 +2135,7 @@
       <c r="L28" s="11"/>
       <c r="M28" s="11"/>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="str">
         <f>IF(ISBLANK(interventions!A29),"",interventions!A29)</f>
         <v/>
@@ -2105,7 +2153,7 @@
       <c r="L29" s="11"/>
       <c r="M29" s="11"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="str">
         <f>IF(ISBLANK(interventions!A30),"",interventions!A30)</f>
         <v/>
@@ -2123,7 +2171,7 @@
       <c r="L30" s="11"/>
       <c r="M30" s="11"/>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="str">
         <f>IF(ISBLANK(interventions!A31),"",interventions!A31)</f>
         <v/>
@@ -2141,7 +2189,7 @@
       <c r="L31" s="11"/>
       <c r="M31" s="11"/>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="str">
         <f>IF(ISBLANK(interventions!A32),"",interventions!A32)</f>
         <v/>
@@ -2159,7 +2207,7 @@
       <c r="L32" s="11"/>
       <c r="M32" s="11"/>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="str">
         <f>IF(ISBLANK(interventions!A33),"",interventions!A33)</f>
         <v/>
@@ -2177,7 +2225,7 @@
       <c r="L33" s="11"/>
       <c r="M33" s="11"/>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="str">
         <f>IF(ISBLANK(interventions!A34),"",interventions!A34)</f>
         <v/>
@@ -2195,7 +2243,7 @@
       <c r="L34" s="11"/>
       <c r="M34" s="11"/>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="str">
         <f>IF(ISBLANK(interventions!A35),"",interventions!A35)</f>
         <v/>
@@ -2213,7 +2261,7 @@
       <c r="L35" s="11"/>
       <c r="M35" s="11"/>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="str">
         <f>IF(ISBLANK(interventions!A36),"",interventions!A36)</f>
         <v/>
@@ -2231,7 +2279,7 @@
       <c r="L36" s="11"/>
       <c r="M36" s="11"/>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="str">
         <f>IF(ISBLANK(interventions!A37),"",interventions!A37)</f>
         <v/>
@@ -2249,7 +2297,7 @@
       <c r="L37" s="11"/>
       <c r="M37" s="11"/>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="str">
         <f>IF(ISBLANK(interventions!A38),"",interventions!A38)</f>
         <v/>
@@ -2267,7 +2315,7 @@
       <c r="L38" s="11"/>
       <c r="M38" s="11"/>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="str">
         <f>IF(ISBLANK(interventions!A39),"",interventions!A39)</f>
         <v/>
@@ -2285,7 +2333,7 @@
       <c r="L39" s="11"/>
       <c r="M39" s="11"/>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="str">
         <f>IF(ISBLANK(interventions!A40),"",interventions!A40)</f>
         <v/>
@@ -2303,7 +2351,7 @@
       <c r="L40" s="11"/>
       <c r="M40" s="11"/>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="str">
         <f>IF(ISBLANK(interventions!A41),"",interventions!A41)</f>
         <v/>
@@ -2321,7 +2369,7 @@
       <c r="L41" s="11"/>
       <c r="M41" s="11"/>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="str">
         <f>IF(ISBLANK(interventions!A42),"",interventions!A42)</f>
         <v/>
@@ -2339,7 +2387,7 @@
       <c r="L42" s="11"/>
       <c r="M42" s="11"/>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="str">
         <f>IF(ISBLANK(interventions!A43),"",interventions!A43)</f>
         <v/>
@@ -2357,7 +2405,7 @@
       <c r="L43" s="11"/>
       <c r="M43" s="11"/>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="str">
         <f>IF(ISBLANK(interventions!A44),"",interventions!A44)</f>
         <v/>
@@ -2375,7 +2423,7 @@
       <c r="L44" s="11"/>
       <c r="M44" s="11"/>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="str">
         <f>IF(ISBLANK(interventions!A45),"",interventions!A45)</f>
         <v/>
@@ -2393,7 +2441,7 @@
       <c r="L45" s="11"/>
       <c r="M45" s="11"/>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="str">
         <f>IF(ISBLANK(interventions!A46),"",interventions!A46)</f>
         <v/>
@@ -2411,7 +2459,7 @@
       <c r="L46" s="11"/>
       <c r="M46" s="11"/>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="str">
         <f>IF(ISBLANK(interventions!A47),"",interventions!A47)</f>
         <v/>
@@ -2431,7 +2479,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:M47">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+      <formula>"y"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N4:O9">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"y"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2443,20 +2496,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EDB1B9B-545D-4297-BB39-C50701A07DD3}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:K47"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.1796875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2486,7 +2539,7 @@
       </c>
       <c r="K1" s="8"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="str">
         <f>IF(ISBLANK(interventions!A2),"",interventions!A2)</f>
         <v>pwid_vax</v>
@@ -2498,7 +2551,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="str">
         <f>IF(ISBLANK(interventions!A3),"",interventions!A3)</f>
         <v>pwid_vax_campaign</v>
@@ -2519,7 +2572,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="14" t="str">
         <f>IF(ISBLANK(interventions!A4),"",interventions!A4)</f>
         <v>prison_vax_campaign</v>
@@ -2540,7 +2593,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="str">
         <f>IF(ISBLANK(interventions!A5),"",interventions!A5)</f>
         <v>teen_vax</v>
@@ -2552,7 +2605,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="str">
         <f>IF(ISBLANK(interventions!A6),"",interventions!A6)</f>
         <v>adults_vax</v>
@@ -2564,7 +2617,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="str">
         <f>IF(ISBLANK(interventions!A7),"",interventions!A7)</f>
         <v>pwid_counter</v>
@@ -2585,7 +2638,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="str">
         <f>IF(ISBLANK(interventions!A8),"",interventions!A8)</f>
         <v>prison_counter</v>
@@ -2606,7 +2659,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="str">
         <f>IF(ISBLANK(interventions!A9),"",interventions!A9)</f>
         <v>status_quo</v>
@@ -2636,231 +2689,231 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="str">
         <f>IF(ISBLANK(interventions!A10),"",interventions!A10)</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="str">
         <f>IF(ISBLANK(interventions!A11),"",interventions!A11)</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="str">
         <f>IF(ISBLANK(interventions!A12),"",interventions!A12)</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="str">
         <f>IF(ISBLANK(interventions!A13),"",interventions!A13)</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="str">
         <f>IF(ISBLANK(interventions!A14),"",interventions!A14)</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="str">
         <f>IF(ISBLANK(interventions!A15),"",interventions!A15)</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="str">
         <f>IF(ISBLANK(interventions!A16),"",interventions!A16)</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="str">
         <f>IF(ISBLANK(interventions!A17),"",interventions!A17)</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="str">
         <f>IF(ISBLANK(interventions!A18),"",interventions!A18)</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="str">
         <f>IF(ISBLANK(interventions!A19),"",interventions!A19)</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="str">
         <f>IF(ISBLANK(interventions!A20),"",interventions!A20)</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="str">
         <f>IF(ISBLANK(interventions!A21),"",interventions!A21)</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="str">
         <f>IF(ISBLANK(interventions!A22),"",interventions!A22)</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="str">
         <f>IF(ISBLANK(interventions!A23),"",interventions!A23)</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="str">
         <f>IF(ISBLANK(interventions!A24),"",interventions!A24)</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="str">
         <f>IF(ISBLANK(interventions!A25),"",interventions!A25)</f>
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="str">
         <f>IF(ISBLANK(interventions!A26),"",interventions!A26)</f>
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="str">
         <f>IF(ISBLANK(interventions!A27),"",interventions!A27)</f>
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="str">
         <f>IF(ISBLANK(interventions!A28),"",interventions!A28)</f>
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="str">
         <f>IF(ISBLANK(interventions!A29),"",interventions!A29)</f>
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="str">
         <f>IF(ISBLANK(interventions!A30),"",interventions!A30)</f>
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="str">
         <f>IF(ISBLANK(interventions!A31),"",interventions!A31)</f>
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="str">
         <f>IF(ISBLANK(interventions!A32),"",interventions!A32)</f>
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="str">
         <f>IF(ISBLANK(interventions!A33),"",interventions!A33)</f>
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="str">
         <f>IF(ISBLANK(interventions!A34),"",interventions!A34)</f>
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="str">
         <f>IF(ISBLANK(interventions!A35),"",interventions!A35)</f>
         <v/>
       </c>
       <c r="D35" s="6"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="str">
         <f>IF(ISBLANK(interventions!A36),"",interventions!A36)</f>
         <v/>
       </c>
       <c r="D36" s="6"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="str">
         <f>IF(ISBLANK(interventions!A37),"",interventions!A37)</f>
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="str">
         <f>IF(ISBLANK(interventions!A38),"",interventions!A38)</f>
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="str">
         <f>IF(ISBLANK(interventions!A39),"",interventions!A39)</f>
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="str">
         <f>IF(ISBLANK(interventions!A40),"",interventions!A40)</f>
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="str">
         <f>IF(ISBLANK(interventions!A41),"",interventions!A41)</f>
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="str">
         <f>IF(ISBLANK(interventions!A42),"",interventions!A42)</f>
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="str">
         <f>IF(ISBLANK(interventions!A43),"",interventions!A43)</f>
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="str">
         <f>IF(ISBLANK(interventions!A44),"",interventions!A44)</f>
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="str">
         <f>IF(ISBLANK(interventions!A45),"",interventions!A45)</f>
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="str">
         <f>IF(ISBLANK(interventions!A46),"",interventions!A46)</f>
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="str">
         <f>IF(ISBLANK(interventions!A47),"",interventions!A47)</f>
         <v/>
@@ -2868,7 +2921,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:I31">
-    <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="7" operator="equal">
       <formula>"y"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2881,20 +2934,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{193E247F-181A-4B6D-B2CD-717659CE10EB}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:J47"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2926,7 +2979,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="str">
         <f>IF(ISBLANK(interventions!A2),"",interventions!A2)</f>
         <v>pwid_vax</v>
@@ -2947,7 +3000,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="str">
         <f>IF(ISBLANK(interventions!A3),"",interventions!A3)</f>
         <v>pwid_vax_campaign</v>
@@ -2968,7 +3021,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="str">
         <f>IF(ISBLANK(interventions!A4),"",interventions!A4)</f>
         <v>prison_vax_campaign</v>
@@ -2990,7 +3043,7 @@
       </c>
       <c r="J4" s="9"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="str">
         <f>IF(ISBLANK(interventions!A5),"",interventions!A5)</f>
         <v>teen_vax</v>
@@ -3011,7 +3064,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="str">
         <f>IF(ISBLANK(interventions!A6),"",interventions!A6)</f>
         <v>adults_vax</v>
@@ -3032,7 +3085,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="str">
         <f>IF(ISBLANK(interventions!A7),"",interventions!A7)</f>
         <v>pwid_counter</v>
@@ -3053,7 +3106,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="str">
         <f>IF(ISBLANK(interventions!A8),"",interventions!A8)</f>
         <v>prison_counter</v>
@@ -3074,7 +3127,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="str">
         <f>IF(ISBLANK(interventions!A9),"",interventions!A9)</f>
         <v>status_quo</v>
@@ -3095,7 +3148,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="str">
         <f>IF(ISBLANK(interventions!A10),"",interventions!A10)</f>
         <v/>
@@ -3105,7 +3158,7 @@
       <c r="D10" s="2"/>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="str">
         <f>IF(ISBLANK(interventions!A11),"",interventions!A11)</f>
         <v/>
@@ -3115,7 +3168,7 @@
       <c r="D11" s="2"/>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="str">
         <f>IF(ISBLANK(interventions!A12),"",interventions!A12)</f>
         <v/>
@@ -3125,7 +3178,7 @@
       <c r="D12" s="2"/>
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="str">
         <f>IF(ISBLANK(interventions!A13),"",interventions!A13)</f>
         <v/>
@@ -3135,7 +3188,7 @@
       <c r="D13" s="2"/>
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="str">
         <f>IF(ISBLANK(interventions!A14),"",interventions!A14)</f>
         <v/>
@@ -3145,7 +3198,7 @@
       <c r="D14" s="2"/>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="str">
         <f>IF(ISBLANK(interventions!A15),"",interventions!A15)</f>
         <v/>
@@ -3155,7 +3208,7 @@
       <c r="D15" s="2"/>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="str">
         <f>IF(ISBLANK(interventions!A16),"",interventions!A16)</f>
         <v/>
@@ -3165,7 +3218,7 @@
       <c r="D16" s="2"/>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="str">
         <f>IF(ISBLANK(interventions!A17),"",interventions!A17)</f>
         <v/>
@@ -3175,7 +3228,7 @@
       <c r="D17" s="2"/>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="str">
         <f>IF(ISBLANK(interventions!A18),"",interventions!A18)</f>
         <v/>
@@ -3185,7 +3238,7 @@
       <c r="D18" s="2"/>
       <c r="E18" s="1"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="str">
         <f>IF(ISBLANK(interventions!A19),"",interventions!A19)</f>
         <v/>
@@ -3195,7 +3248,7 @@
       <c r="D19" s="2"/>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="str">
         <f>IF(ISBLANK(interventions!A20),"",interventions!A20)</f>
         <v/>
@@ -3205,7 +3258,7 @@
       <c r="D20" s="2"/>
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="str">
         <f>IF(ISBLANK(interventions!A21),"",interventions!A21)</f>
         <v/>
@@ -3215,7 +3268,7 @@
       <c r="D21" s="2"/>
       <c r="E21" s="1"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="str">
         <f>IF(ISBLANK(interventions!A22),"",interventions!A22)</f>
         <v/>
@@ -3225,7 +3278,7 @@
       <c r="D22" s="2"/>
       <c r="E22" s="1"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="str">
         <f>IF(ISBLANK(interventions!A23),"",interventions!A23)</f>
         <v/>
@@ -3235,7 +3288,7 @@
       <c r="D23" s="2"/>
       <c r="E23" s="1"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="str">
         <f>IF(ISBLANK(interventions!A24),"",interventions!A24)</f>
         <v/>
@@ -3245,7 +3298,7 @@
       <c r="D24" s="2"/>
       <c r="E24" s="1"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="str">
         <f>IF(ISBLANK(interventions!A25),"",interventions!A25)</f>
         <v/>
@@ -3255,7 +3308,7 @@
       <c r="D25" s="2"/>
       <c r="E25" s="1"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="str">
         <f>IF(ISBLANK(interventions!A26),"",interventions!A26)</f>
         <v/>
@@ -3265,7 +3318,7 @@
       <c r="D26" s="2"/>
       <c r="E26" s="1"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="str">
         <f>IF(ISBLANK(interventions!A27),"",interventions!A27)</f>
         <v/>
@@ -3275,7 +3328,7 @@
       <c r="D27" s="2"/>
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="str">
         <f>IF(ISBLANK(interventions!A28),"",interventions!A28)</f>
         <v/>
@@ -3285,7 +3338,7 @@
       <c r="D28" s="2"/>
       <c r="E28" s="1"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="str">
         <f>IF(ISBLANK(interventions!A29),"",interventions!A29)</f>
         <v/>
@@ -3295,7 +3348,7 @@
       <c r="D29" s="2"/>
       <c r="E29" s="1"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="str">
         <f>IF(ISBLANK(interventions!A30),"",interventions!A30)</f>
         <v/>
@@ -3305,7 +3358,7 @@
       <c r="D30" s="2"/>
       <c r="E30" s="1"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="str">
         <f>IF(ISBLANK(interventions!A31),"",interventions!A31)</f>
         <v/>
@@ -3315,7 +3368,7 @@
       <c r="D31" s="2"/>
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="str">
         <f>IF(ISBLANK(interventions!A32),"",interventions!A32)</f>
         <v/>
@@ -3324,7 +3377,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="str">
         <f>IF(ISBLANK(interventions!A33),"",interventions!A33)</f>
         <v/>
@@ -3333,7 +3386,7 @@
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="str">
         <f>IF(ISBLANK(interventions!A34),"",interventions!A34)</f>
         <v/>
@@ -3342,7 +3395,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="str">
         <f>IF(ISBLANK(interventions!A35),"",interventions!A35)</f>
         <v/>
@@ -3351,7 +3404,7 @@
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="str">
         <f>IF(ISBLANK(interventions!A36),"",interventions!A36)</f>
         <v/>
@@ -3360,7 +3413,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="str">
         <f>IF(ISBLANK(interventions!A37),"",interventions!A37)</f>
         <v/>
@@ -3369,7 +3422,7 @@
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="str">
         <f>IF(ISBLANK(interventions!A38),"",interventions!A38)</f>
         <v/>
@@ -3378,7 +3431,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="str">
         <f>IF(ISBLANK(interventions!A39),"",interventions!A39)</f>
         <v/>
@@ -3387,7 +3440,7 @@
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="str">
         <f>IF(ISBLANK(interventions!A40),"",interventions!A40)</f>
         <v/>
@@ -3396,7 +3449,7 @@
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="str">
         <f>IF(ISBLANK(interventions!A41),"",interventions!A41)</f>
         <v/>
@@ -3405,7 +3458,7 @@
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="str">
         <f>IF(ISBLANK(interventions!A42),"",interventions!A42)</f>
         <v/>
@@ -3414,7 +3467,7 @@
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="str">
         <f>IF(ISBLANK(interventions!A43),"",interventions!A43)</f>
         <v/>
@@ -3423,7 +3476,7 @@
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="str">
         <f>IF(ISBLANK(interventions!A44),"",interventions!A44)</f>
         <v/>
@@ -3432,7 +3485,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="str">
         <f>IF(ISBLANK(interventions!A45),"",interventions!A45)</f>
         <v/>
@@ -3441,7 +3494,7 @@
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="str">
         <f>IF(ISBLANK(interventions!A46),"",interventions!A46)</f>
         <v/>
@@ -3450,7 +3503,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="str">
         <f>IF(ISBLANK(interventions!A47),"",interventions!A47)</f>
         <v/>
@@ -3474,26 +3527,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B5232EA-A822-4ED1-B8AA-05F696E2FA18}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:O47"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.5703125" customWidth="1"/>
+    <col min="1" max="1" width="26.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.7265625" customWidth="1"/>
+    <col min="11" max="11" width="20.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.7265625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -3536,7 +3589,7 @@
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="str">
         <f>IF(ISBLANK(interventions!A2),"",interventions!A2)</f>
         <v>pwid_vax</v>
@@ -3548,7 +3601,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="str">
         <f>IF(ISBLANK(interventions!A3),"",interventions!A3)</f>
         <v>pwid_vax_campaign</v>
@@ -3578,7 +3631,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="str">
         <f>IF(ISBLANK(interventions!A4),"",interventions!A4)</f>
         <v>prison_vax_campaign</v>
@@ -3608,7 +3661,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="str">
         <f>IF(ISBLANK(interventions!A5),"",interventions!A5)</f>
         <v>teen_vax</v>
@@ -3620,7 +3673,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="str">
         <f>IF(ISBLANK(interventions!A6),"",interventions!A6)</f>
         <v>adults_vax</v>
@@ -3632,7 +3685,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="str">
         <f>IF(ISBLANK(interventions!A7),"",interventions!A7)</f>
         <v>pwid_counter</v>
@@ -3656,7 +3709,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="str">
         <f>IF(ISBLANK(interventions!A8),"",interventions!A8)</f>
         <v>prison_counter</v>
@@ -3680,241 +3733,241 @@
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="str">
         <f>IF(ISBLANK(interventions!A9),"",interventions!A9)</f>
         <v>status_quo</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="str">
         <f>IF(ISBLANK(interventions!A10),"",interventions!A10)</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="str">
         <f>IF(ISBLANK(interventions!A11),"",interventions!A11)</f>
         <v/>
       </c>
       <c r="H11" s="5"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="str">
         <f>IF(ISBLANK(interventions!A12),"",interventions!A12)</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="str">
         <f>IF(ISBLANK(interventions!A13),"",interventions!A13)</f>
         <v/>
       </c>
       <c r="H13" s="5"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="str">
         <f>IF(ISBLANK(interventions!A14),"",interventions!A14)</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="str">
         <f>IF(ISBLANK(interventions!A15),"",interventions!A15)</f>
         <v/>
       </c>
       <c r="H15" s="5"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="str">
         <f>IF(ISBLANK(interventions!A16),"",interventions!A16)</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="str">
         <f>IF(ISBLANK(interventions!A17),"",interventions!A17)</f>
         <v/>
       </c>
       <c r="H17" s="5"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="str">
         <f>IF(ISBLANK(interventions!A18),"",interventions!A18)</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="str">
         <f>IF(ISBLANK(interventions!A19),"",interventions!A19)</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="str">
         <f>IF(ISBLANK(interventions!A20),"",interventions!A20)</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="str">
         <f>IF(ISBLANK(interventions!A21),"",interventions!A21)</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="str">
         <f>IF(ISBLANK(interventions!A22),"",interventions!A22)</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="str">
         <f>IF(ISBLANK(interventions!A23),"",interventions!A23)</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="str">
         <f>IF(ISBLANK(interventions!A24),"",interventions!A24)</f>
         <v/>
       </c>
       <c r="H24" s="5"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="str">
         <f>IF(ISBLANK(interventions!A25),"",interventions!A25)</f>
         <v/>
       </c>
       <c r="H25" s="5"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="str">
         <f>IF(ISBLANK(interventions!A26),"",interventions!A26)</f>
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="str">
         <f>IF(ISBLANK(interventions!A27),"",interventions!A27)</f>
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="str">
         <f>IF(ISBLANK(interventions!A28),"",interventions!A28)</f>
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="str">
         <f>IF(ISBLANK(interventions!A29),"",interventions!A29)</f>
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="str">
         <f>IF(ISBLANK(interventions!A30),"",interventions!A30)</f>
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="str">
         <f>IF(ISBLANK(interventions!A31),"",interventions!A31)</f>
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="str">
         <f>IF(ISBLANK(interventions!A32),"",interventions!A32)</f>
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="str">
         <f>IF(ISBLANK(interventions!A33),"",interventions!A33)</f>
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="str">
         <f>IF(ISBLANK(interventions!A34),"",interventions!A34)</f>
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="str">
         <f>IF(ISBLANK(interventions!A35),"",interventions!A35)</f>
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="str">
         <f>IF(ISBLANK(interventions!A36),"",interventions!A36)</f>
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="str">
         <f>IF(ISBLANK(interventions!A37),"",interventions!A37)</f>
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="str">
         <f>IF(ISBLANK(interventions!A38),"",interventions!A38)</f>
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="str">
         <f>IF(ISBLANK(interventions!A39),"",interventions!A39)</f>
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="str">
         <f>IF(ISBLANK(interventions!A40),"",interventions!A40)</f>
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="str">
         <f>IF(ISBLANK(interventions!A41),"",interventions!A41)</f>
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="str">
         <f>IF(ISBLANK(interventions!A42),"",interventions!A42)</f>
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="str">
         <f>IF(ISBLANK(interventions!A43),"",interventions!A43)</f>
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="str">
         <f>IF(ISBLANK(interventions!A44),"",interventions!A44)</f>
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="str">
         <f>IF(ISBLANK(interventions!A45),"",interventions!A45)</f>
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="str">
         <f>IF(ISBLANK(interventions!A46),"",interventions!A46)</f>
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="str">
         <f>IF(ISBLANK(interventions!A47),"",interventions!A47)</f>
         <v/>
@@ -3935,17 +3988,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C010CA95-9913-4E01-BBC8-E12EAEB492A2}">
   <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="44.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.26953125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="27" t="s">
         <v>55</v>
       </c>
@@ -3965,7 +4018,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="15" t="s">
         <v>71</v>
       </c>
@@ -3982,7 +4035,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="30" t="s">
         <v>72</v>
       </c>
@@ -4000,7 +4053,7 @@
       </c>
       <c r="F3" s="31"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="28" t="s">
         <v>73</v>
       </c>
@@ -4018,7 +4071,7 @@
       </c>
       <c r="F4" s="29"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="26" t="s">
         <v>73</v>
       </c>
@@ -4036,7 +4089,7 @@
       </c>
       <c r="F5" s="21"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="25" t="s">
         <v>74</v>
       </c>
@@ -4056,7 +4109,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
         <v>75</v>
       </c>
@@ -4076,7 +4129,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="24" t="s">
         <v>75</v>
       </c>
@@ -4094,7 +4147,7 @@
       </c>
       <c r="F8" s="21"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="17" t="s">
         <v>76</v>
       </c>
@@ -4114,7 +4167,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="17" t="s">
         <v>76</v>
       </c>
@@ -4131,7 +4184,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="23" t="s">
         <v>76</v>
       </c>
@@ -4149,7 +4202,7 @@
       </c>
       <c r="F11" s="21"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="18" t="s">
         <v>77</v>
       </c>
@@ -4169,7 +4222,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="18" t="s">
         <v>77</v>
       </c>
@@ -4186,7 +4239,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="18" t="s">
         <v>77</v>
       </c>
@@ -4203,7 +4256,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="20" t="s">
         <v>77</v>
       </c>
@@ -4221,7 +4274,7 @@
       </c>
       <c r="F15" s="21"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="19" t="s">
         <v>78</v>
       </c>
@@ -4241,7 +4294,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="19" t="s">
         <v>78</v>
       </c>
@@ -4258,7 +4311,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="19" t="s">
         <v>78</v>
       </c>
@@ -4275,7 +4328,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="19" t="s">
         <v>78</v>
       </c>
@@ -4292,7 +4345,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="22" t="s">
         <v>78</v>
       </c>
@@ -4319,25 +4372,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="460e4ad2-c64b-4f67-8552-094351f252e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010042DC9346A4EFF44B9278E035670E998A" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b6002ac4d6852791cc52372fb08f1f93">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="460e4ad2-c64b-4f67-8552-094351f252e3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d81800e77b8320248f69566da91fdce8" ns2:_="">
     <xsd:import namespace="460e4ad2-c64b-4f67-8552-094351f252e3"/>
@@ -4509,31 +4543,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA2D8656-6848-4E43-8697-69A82BA725E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="460e4ad2-c64b-4f67-8552-094351f252e3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3882B21-9C06-4A25-BA73-35DB35426A28}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="460e4ad2-c64b-4f67-8552-094351f252e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090DCA50-A1C8-4B02-A520-4AE25ED4C282}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4549,4 +4578,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3882B21-9C06-4A25-BA73-35DB35426A28}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA2D8656-6848-4E43-8697-69A82BA725E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="460e4ad2-c64b-4f67-8552-094351f252e3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/progbook_inputs.xlsx
+++ b/data/progbook_inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farah.houdroge\Documents\GitHub\hcv-vaccine\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A436CEC3-1484-4EF8-A944-DB4460F853F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C891FB-A134-461E-84AC-8A521218CD9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E2E90E70-2F54-4097-8786-78C8F6F97317}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{E2E90E70-2F54-4097-8786-78C8F6F97317}"/>
   </bookViews>
   <sheets>
     <sheet name="interventions" sheetId="7" r:id="rId1"/>
@@ -482,7 +482,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="95">
   <si>
     <t>code</t>
   </si>
@@ -616,9 +616,6 @@
     <t>PWID – Vaccine + Test &amp; Treat scale-up</t>
   </si>
   <si>
-    <t>Prisoners – Vaccine + Test &amp; Treat scale-up</t>
-  </si>
-  <si>
     <t>Adolescents – School-based vaccination</t>
   </si>
   <si>
@@ -730,19 +727,46 @@
     <t>PWID + Campaign</t>
   </si>
   <si>
-    <t>PWID + Campaign + Prison</t>
-  </si>
-  <si>
-    <t>PWID + Campaign + Prison + Schools</t>
-  </si>
-  <si>
-    <t>PWID + Campaign + Prison + Schools + Adults</t>
-  </si>
-  <si>
     <t>Prisoners_PWID_males</t>
   </si>
   <si>
     <t>Prisoners_PWID_females</t>
+  </si>
+  <si>
+    <t>prison_vax_campaign_all</t>
+  </si>
+  <si>
+    <t>All prisoners – Vaccine + Test &amp; Treat scale-up</t>
+  </si>
+  <si>
+    <t>PWID prisoners – Vaccine + Test &amp; Treat scale-up</t>
+  </si>
+  <si>
+    <t>scenario_5</t>
+  </si>
+  <si>
+    <t>PWID + Campaign + PWID Prison</t>
+  </si>
+  <si>
+    <t>prison_counter_all</t>
+  </si>
+  <si>
+    <t>Counterfactual scenario for all prisoners test&amp;treat scale-up</t>
+  </si>
+  <si>
+    <t>PWID + Campaign + All Prisoners</t>
+  </si>
+  <si>
+    <t>counter_3</t>
+  </si>
+  <si>
+    <t>PWID + Prison All Counterfactual</t>
+  </si>
+  <si>
+    <t>PWID + Campaign + PWID Prison + Schools</t>
+  </si>
+  <si>
+    <t>PWID + Campaign + PWID Prison + Schools + Adults</t>
   </si>
 </sst>
 </file>
@@ -1006,7 +1030,17 @@
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1389,7 +1423,7 @@
         <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -1397,7 +1431,7 @@
         <v>37</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -1405,38 +1439,48 @@
         <v>41</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="3"/>
+      <c r="A10" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" s="3"/>
+      <c r="A11" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B11" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="3"/>
@@ -1567,10 +1611,10 @@
         <v>36</v>
       </c>
       <c r="N1" s="10" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O1" s="10" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.35">
@@ -1632,12 +1676,8 @@
       <c r="I4" s="11"/>
       <c r="J4" s="11"/>
       <c r="K4" s="11"/>
-      <c r="L4" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="M4" s="11" t="s">
-        <v>15</v>
-      </c>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
       <c r="N4" s="11" t="s">
         <v>15</v>
       </c>
@@ -1732,12 +1772,8 @@
       <c r="I8" s="11"/>
       <c r="J8" s="11"/>
       <c r="K8" s="11"/>
-      <c r="L8" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="M8" s="11" t="s">
-        <v>15</v>
-      </c>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
       <c r="N8" s="11" t="s">
         <v>15</v>
       </c>
@@ -1796,7 +1832,7 @@
     <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="str">
         <f>IF(ISBLANK(interventions!A10),"",interventions!A10)</f>
-        <v/>
+        <v>prison_vax_campaign_all</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -1808,13 +1844,23 @@
       <c r="I10" s="11"/>
       <c r="J10" s="11"/>
       <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
+      <c r="L10" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="N10" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="O10" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="str">
         <f>IF(ISBLANK(interventions!A11),"",interventions!A11)</f>
-        <v/>
+        <v>prison_counter_all</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -1826,8 +1872,18 @@
       <c r="I11" s="11"/>
       <c r="J11" s="11"/>
       <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
+      <c r="L11" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="N11" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="O11" s="11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="str">
@@ -2479,12 +2535,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:M47">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+      <formula>"y"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N4:O9">
     <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"y"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N4:O9">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+  <conditionalFormatting sqref="N10:O11">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"y"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2692,13 +2753,43 @@
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="str">
         <f>IF(ISBLANK(interventions!A10),"",interventions!A10)</f>
-        <v/>
+        <v>prison_vax_campaign_all</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="str">
         <f>IF(ISBLANK(interventions!A11),"",interventions!A11)</f>
-        <v/>
+        <v>prison_counter_all</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
@@ -2921,7 +3012,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:I31">
-    <cfRule type="cellIs" dxfId="1" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
       <formula>"y"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2952,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>4</v>
@@ -3151,22 +3242,44 @@
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="str">
         <f>IF(ISBLANK(interventions!A10),"",interventions!A10)</f>
-        <v/>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="1"/>
+        <v>prison_vax_campaign_all</v>
+      </c>
+      <c r="B10" s="13">
+        <v>10</v>
+      </c>
+      <c r="C10" s="13">
+        <v>20</v>
+      </c>
+      <c r="D10" s="13">
+        <v>30</v>
+      </c>
+      <c r="E10" s="13">
+        <v>40</v>
+      </c>
+      <c r="F10" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="str">
         <f>IF(ISBLANK(interventions!A11),"",interventions!A11)</f>
-        <v/>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="1"/>
+        <v>prison_counter_all</v>
+      </c>
+      <c r="B11" s="13">
+        <v>10</v>
+      </c>
+      <c r="C11" s="13">
+        <v>20</v>
+      </c>
+      <c r="D11" s="13">
+        <v>30</v>
+      </c>
+      <c r="E11" s="13">
+        <v>40</v>
+      </c>
+      <c r="F11" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="str">
@@ -3575,16 +3688,16 @@
         <v>17</v>
       </c>
       <c r="J1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="K1" s="4" t="s">
-        <v>52</v>
-      </c>
       <c r="L1" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M1" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>60</v>
       </c>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
@@ -3595,10 +3708,10 @@
         <v>pwid_vax</v>
       </c>
       <c r="J2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.35">
@@ -3610,25 +3723,25 @@
         <v>0.8</v>
       </c>
       <c r="E3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F3">
         <v>0.8</v>
       </c>
       <c r="G3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H3">
         <v>0.8</v>
       </c>
       <c r="I3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J3">
         <v>0.8</v>
       </c>
       <c r="K3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.35">
@@ -3640,25 +3753,25 @@
         <v>0.8</v>
       </c>
       <c r="E4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F4">
         <v>0.8</v>
       </c>
       <c r="G4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H4">
         <v>0.8</v>
       </c>
       <c r="I4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J4">
         <v>0.8</v>
       </c>
       <c r="K4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.35">
@@ -3667,10 +3780,10 @@
         <v>teen_vax</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.35">
@@ -3682,7 +3795,7 @@
         <v>0.8</v>
       </c>
       <c r="K6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.35">
@@ -3694,19 +3807,19 @@
         <v>0.8</v>
       </c>
       <c r="E7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F7">
         <v>0.8</v>
       </c>
       <c r="G7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H7">
         <v>0.8</v>
       </c>
       <c r="I7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.35">
@@ -3718,19 +3831,19 @@
         <v>0.8</v>
       </c>
       <c r="E8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F8">
         <v>0.8</v>
       </c>
       <c r="G8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H8">
         <v>0.8</v>
       </c>
       <c r="I8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.35">
@@ -3742,15 +3855,56 @@
     <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="str">
         <f>IF(ISBLANK(interventions!A10),"",interventions!A10)</f>
-        <v/>
+        <v>prison_vax_campaign_all</v>
+      </c>
+      <c r="D10">
+        <v>0.8</v>
+      </c>
+      <c r="E10" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10">
+        <v>0.8</v>
+      </c>
+      <c r="G10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10">
+        <v>0.8</v>
+      </c>
+      <c r="I10" t="s">
+        <v>52</v>
+      </c>
+      <c r="J10">
+        <v>0.8</v>
+      </c>
+      <c r="K10" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="str">
         <f>IF(ISBLANK(interventions!A11),"",interventions!A11)</f>
-        <v/>
-      </c>
-      <c r="H11" s="5"/>
+        <v>prison_counter_all</v>
+      </c>
+      <c r="D11">
+        <v>0.8</v>
+      </c>
+      <c r="E11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F11">
+        <v>0.8</v>
+      </c>
+      <c r="G11" t="s">
+        <v>52</v>
+      </c>
+      <c r="H11">
+        <v>0.8</v>
+      </c>
+      <c r="I11" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="str">
@@ -3975,7 +4129,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C47 M2:M47 K2:K47 I2:I47 E2:E47 G2:G47" xr:uid="{9A136EE2-9E44-426F-8888-910675484DBA}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M47 C2:C47 K2:K47 I2:I47 E2:E47 G2:G47" xr:uid="{9A136EE2-9E44-426F-8888-910675484DBA}">
       <formula1>"RR, OR, PROB"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3987,12 +4141,12 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C010CA95-9913-4E01-BBC8-E12EAEB492A2}">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="44.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.1796875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.81640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.26953125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
@@ -4000,33 +4154,33 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="C1" s="27" t="s">
+      <c r="D1" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="E1" s="27" t="s">
-        <v>57</v>
-      </c>
       <c r="F1" s="27" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" t="s">
         <v>62</v>
-      </c>
-      <c r="C2" t="s">
-        <v>63</v>
       </c>
       <c r="D2">
         <v>2027</v>
@@ -4037,13 +4191,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D3" s="31">
         <v>2027</v>
@@ -4055,13 +4209,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="28" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D4" s="29">
         <v>2027</v>
@@ -4073,13 +4227,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D5" s="21">
         <v>2027</v>
@@ -4090,69 +4244,67 @@
       <c r="F5" s="21"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="C6" s="21" t="s">
+      <c r="A6" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" s="29">
+        <v>2027</v>
+      </c>
+      <c r="E6" s="29">
+        <v>2028</v>
+      </c>
+      <c r="F6" s="29"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="D7" s="21">
+        <v>2027</v>
+      </c>
+      <c r="E7" s="21">
+        <v>2050</v>
+      </c>
+      <c r="F7" s="21"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="21" t="s">
         <v>38</v>
-      </c>
-      <c r="D6" s="21">
-        <v>2027</v>
-      </c>
-      <c r="E6" s="21">
-        <v>2050</v>
-      </c>
-      <c r="F6" s="21" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7">
-        <v>2028</v>
-      </c>
-      <c r="E7">
-        <v>2050</v>
-      </c>
-      <c r="F7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>39</v>
       </c>
       <c r="D8" s="21">
         <v>2027</v>
       </c>
       <c r="E8" s="21">
-        <v>2028</v>
-      </c>
-      <c r="F8" s="21"/>
+        <v>2050</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="17" t="s">
-        <v>76</v>
+      <c r="A9" s="16" t="s">
+        <v>74</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
         <v>38</v>
@@ -4164,205 +4316,298 @@
         <v>2050</v>
       </c>
       <c r="F9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="B10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="A10" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="21">
         <v>2027</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="21">
         <v>2028</v>
       </c>
+      <c r="F10" s="21"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="B11" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" s="21" t="s">
+      <c r="A11" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11">
+        <v>2028</v>
+      </c>
+      <c r="E11">
+        <v>2050</v>
+      </c>
+      <c r="F11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="B12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12">
+        <v>2027</v>
+      </c>
+      <c r="E12">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="21">
+      <c r="D13" s="21">
         <v>2027</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E13" s="21">
         <v>2050</v>
       </c>
-      <c r="F11" s="21"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="B12" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12">
-        <v>2028</v>
-      </c>
-      <c r="E12">
-        <v>2050</v>
-      </c>
-      <c r="F12" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="B13" t="s">
-        <v>83</v>
-      </c>
-      <c r="C13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13">
-        <v>2027</v>
-      </c>
-      <c r="E13">
-        <v>2028</v>
-      </c>
+      <c r="F13" s="21"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="C14" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D14">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="E14">
         <v>2050</v>
       </c>
+      <c r="F14" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="B15" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="C15" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" s="21">
+      <c r="A15" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15">
         <v>2027</v>
       </c>
-      <c r="E15" s="21">
-        <v>2050</v>
-      </c>
-      <c r="F15" s="21"/>
+      <c r="E15">
+        <v>2028</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="19" t="s">
-        <v>78</v>
+      <c r="A16" s="18" t="s">
+        <v>76</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="C16" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D16">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="E16">
         <v>2050</v>
       </c>
-      <c r="F16" t="s">
-        <v>73</v>
-      </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="B17" t="s">
-        <v>84</v>
-      </c>
-      <c r="C17" t="s">
-        <v>39</v>
-      </c>
-      <c r="D17">
+      <c r="A17" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" s="21">
         <v>2027</v>
       </c>
-      <c r="E17">
-        <v>2028</v>
-      </c>
+      <c r="E17" s="21">
+        <v>2050</v>
+      </c>
+      <c r="F17" s="21"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D18">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="E18">
         <v>2050</v>
       </c>
+      <c r="F18" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D19">
         <v>2027</v>
       </c>
       <c r="E19">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="B20" t="s">
+        <v>94</v>
+      </c>
+      <c r="C20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20">
+        <v>2027</v>
+      </c>
+      <c r="E20">
         <v>2050</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="B20" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="C20" s="21" t="s">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="B21" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21">
+        <v>2027</v>
+      </c>
+      <c r="E21">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="B22" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="C22" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D20" s="21">
+      <c r="D22" s="21">
         <v>2027</v>
       </c>
-      <c r="E20" s="21">
-        <f>D20+5</f>
+      <c r="E22" s="21">
+        <f>D22+5</f>
         <v>2032</v>
       </c>
-      <c r="F20" s="21"/>
+      <c r="F22" s="21"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B23" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23">
+        <v>2028</v>
+      </c>
+      <c r="E23">
+        <v>2050</v>
+      </c>
+      <c r="F23" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24">
+        <v>2027</v>
+      </c>
+      <c r="E24">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C25" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D25" s="21">
+        <v>2027</v>
+      </c>
+      <c r="E25" s="21">
+        <v>2050</v>
+      </c>
+      <c r="F25" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/progbook_inputs.xlsx
+++ b/data/progbook_inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farah.houdroge\Documents\GitHub\hcv-vaccine\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C891FB-A134-461E-84AC-8A521218CD9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3388EFF-6C17-458E-8601-94BC18157DB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{E2E90E70-2F54-4097-8786-78C8F6F97317}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E2E90E70-2F54-4097-8786-78C8F6F97317}"/>
   </bookViews>
   <sheets>
     <sheet name="interventions" sheetId="7" r:id="rId1"/>
@@ -482,7 +482,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="87">
   <si>
     <t>code</t>
   </si>
@@ -733,40 +733,16 @@
     <t>Prisoners_PWID_females</t>
   </si>
   <si>
-    <t>prison_vax_campaign_all</t>
-  </si>
-  <si>
-    <t>All prisoners – Vaccine + Test &amp; Treat scale-up</t>
-  </si>
-  <si>
     <t>PWID prisoners – Vaccine + Test &amp; Treat scale-up</t>
   </si>
   <si>
-    <t>scenario_5</t>
-  </si>
-  <si>
-    <t>PWID + Campaign + PWID Prison</t>
-  </si>
-  <si>
-    <t>prison_counter_all</t>
-  </si>
-  <si>
-    <t>Counterfactual scenario for all prisoners test&amp;treat scale-up</t>
-  </si>
-  <si>
-    <t>PWID + Campaign + All Prisoners</t>
-  </si>
-  <si>
-    <t>counter_3</t>
-  </si>
-  <si>
-    <t>PWID + Prison All Counterfactual</t>
-  </si>
-  <si>
-    <t>PWID + Campaign + PWID Prison + Schools</t>
-  </si>
-  <si>
-    <t>PWID + Campaign + PWID Prison + Schools + Adults</t>
+    <t>PWID + Campaign + Prison</t>
+  </si>
+  <si>
+    <t>PWID + Campaign + Prison + Schools</t>
+  </si>
+  <si>
+    <t>PWID + Campaign + Prison + Schools + Adults</t>
   </si>
 </sst>
 </file>
@@ -1030,17 +1006,7 @@
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1387,7 +1353,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7293DEF-C325-4FE3-AD5B-B41F22CF0DA3}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.26953125" bestFit="1" customWidth="1"/>
@@ -1423,7 +1389,7 @@
         <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -1467,20 +1433,10 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B10" t="s">
-        <v>84</v>
-      </c>
+      <c r="A10" s="3"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B11" t="s">
-        <v>89</v>
-      </c>
+      <c r="A11" s="3"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="3"/>
@@ -1528,19 +1484,13 @@
       <c r="A26" s="3"/>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A27" s="3"/>
+      <c r="A27" s="4"/>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A28" s="3"/>
+      <c r="A28" s="4"/>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A29" s="4"/>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A30" s="4"/>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A31" s="3"/>
+      <c r="A29" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1550,7 +1500,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01B95C70-A891-4037-BF3D-C1EB7C57DA84}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:O47"/>
+  <dimension ref="A1:O45"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.26953125" bestFit="1" customWidth="1"/>
@@ -1832,7 +1782,7 @@
     <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="str">
         <f>IF(ISBLANK(interventions!A10),"",interventions!A10)</f>
-        <v>prison_vax_campaign_all</v>
+        <v/>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -1844,23 +1794,13 @@
       <c r="I10" s="11"/>
       <c r="J10" s="11"/>
       <c r="K10" s="11"/>
-      <c r="L10" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="M10" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="N10" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="O10" s="11" t="s">
-        <v>15</v>
-      </c>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="str">
         <f>IF(ISBLANK(interventions!A11),"",interventions!A11)</f>
-        <v>prison_counter_all</v>
+        <v/>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -1872,18 +1812,8 @@
       <c r="I11" s="11"/>
       <c r="J11" s="11"/>
       <c r="K11" s="11"/>
-      <c r="L11" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="M11" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="N11" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="O11" s="11" t="s">
-        <v>15</v>
-      </c>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="str">
@@ -2497,54 +2427,13 @@
       <c r="L45" s="11"/>
       <c r="M45" s="11"/>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A46" s="4" t="str">
-        <f>IF(ISBLANK(interventions!A46),"",interventions!A46)</f>
-        <v/>
-      </c>
-      <c r="B46" s="11"/>
-      <c r="C46" s="11"/>
-      <c r="D46" s="11"/>
-      <c r="E46" s="11"/>
-      <c r="F46" s="11"/>
-      <c r="G46" s="11"/>
-      <c r="H46" s="11"/>
-      <c r="I46" s="11"/>
-      <c r="J46" s="11"/>
-      <c r="K46" s="11"/>
-      <c r="L46" s="11"/>
-      <c r="M46" s="11"/>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A47" s="4" t="str">
-        <f>IF(ISBLANK(interventions!A47),"",interventions!A47)</f>
-        <v/>
-      </c>
-      <c r="B47" s="11"/>
-      <c r="C47" s="11"/>
-      <c r="D47" s="11"/>
-      <c r="E47" s="11"/>
-      <c r="F47" s="11"/>
-      <c r="G47" s="11"/>
-      <c r="H47" s="11"/>
-      <c r="I47" s="11"/>
-      <c r="J47" s="11"/>
-      <c r="K47" s="11"/>
-      <c r="L47" s="11"/>
-      <c r="M47" s="11"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:M47">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+  <conditionalFormatting sqref="B2:M45">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"y"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N4:O9">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
-      <formula>"y"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N10:O11">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"y"</formula>
     </cfRule>
@@ -2556,7 +2445,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EDB1B9B-545D-4297-BB39-C50701A07DD3}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.26953125" bestFit="1" customWidth="1"/>
@@ -2753,43 +2642,13 @@
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="str">
         <f>IF(ISBLANK(interventions!A10),"",interventions!A10)</f>
-        <v>prison_vax_campaign_all</v>
-      </c>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" t="s">
-        <v>15</v>
+        <v/>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="str">
         <f>IF(ISBLANK(interventions!A11),"",interventions!A11)</f>
-        <v>prison_counter_all</v>
-      </c>
-      <c r="B11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" t="s">
-        <v>15</v>
+        <v/>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
@@ -2923,26 +2782,26 @@
         <f>IF(ISBLANK(interventions!A33),"",interventions!A33)</f>
         <v/>
       </c>
+      <c r="D33" s="6"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="str">
         <f>IF(ISBLANK(interventions!A34),"",interventions!A34)</f>
         <v/>
       </c>
+      <c r="D34" s="6"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="str">
         <f>IF(ISBLANK(interventions!A35),"",interventions!A35)</f>
         <v/>
       </c>
-      <c r="D35" s="6"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="str">
         <f>IF(ISBLANK(interventions!A36),"",interventions!A36)</f>
         <v/>
       </c>
-      <c r="D36" s="6"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="str">
@@ -2998,20 +2857,8 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" s="4" t="str">
-        <f>IF(ISBLANK(interventions!A46),"",interventions!A46)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" s="4" t="str">
-        <f>IF(ISBLANK(interventions!A47),"",interventions!A47)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:I31">
+  <conditionalFormatting sqref="B2:I29">
     <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
       <formula>"y"</formula>
     </cfRule>
@@ -3024,7 +2871,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{193E247F-181A-4B6D-B2CD-717659CE10EB}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.26953125" bestFit="1" customWidth="1"/>
@@ -3242,44 +3089,22 @@
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="str">
         <f>IF(ISBLANK(interventions!A10),"",interventions!A10)</f>
-        <v>prison_vax_campaign_all</v>
-      </c>
-      <c r="B10" s="13">
-        <v>10</v>
-      </c>
-      <c r="C10" s="13">
-        <v>20</v>
-      </c>
-      <c r="D10" s="13">
-        <v>30</v>
-      </c>
-      <c r="E10" s="13">
-        <v>40</v>
-      </c>
-      <c r="F10" t="s">
-        <v>5</v>
-      </c>
+        <v/>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="1"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="str">
         <f>IF(ISBLANK(interventions!A11),"",interventions!A11)</f>
-        <v>prison_counter_all</v>
-      </c>
-      <c r="B11" s="13">
-        <v>10</v>
-      </c>
-      <c r="C11" s="13">
-        <v>20</v>
-      </c>
-      <c r="D11" s="13">
-        <v>30</v>
-      </c>
-      <c r="E11" s="13">
-        <v>40</v>
-      </c>
-      <c r="F11" t="s">
-        <v>5</v>
-      </c>
+        <v/>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="1"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="str">
@@ -3469,7 +3294,6 @@
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
-      <c r="E30" s="1"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="str">
@@ -3479,7 +3303,6 @@
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
-      <c r="E31" s="1"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="str">
@@ -3607,27 +3430,9 @@
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" s="4" t="str">
-        <f>IF(ISBLANK(interventions!A46),"",interventions!A46)</f>
-        <v/>
-      </c>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" s="4" t="str">
-        <f>IF(ISBLANK(interventions!A47),"",interventions!A47)</f>
-        <v/>
-      </c>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F31" xr:uid="{705BD241-D3AE-494C-B9B6-56110DA500F1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F29" xr:uid="{705BD241-D3AE-494C-B9B6-56110DA500F1}">
       <formula1>"one-off, continuous"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3639,7 +3444,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B5232EA-A822-4ED1-B8AA-05F696E2FA18}">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:O47"/>
+  <dimension ref="A1:O45"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.26953125" bestFit="1" customWidth="1"/>
@@ -3855,56 +3660,15 @@
     <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="str">
         <f>IF(ISBLANK(interventions!A10),"",interventions!A10)</f>
-        <v>prison_vax_campaign_all</v>
-      </c>
-      <c r="D10">
-        <v>0.8</v>
-      </c>
-      <c r="E10" t="s">
-        <v>52</v>
-      </c>
-      <c r="F10">
-        <v>0.8</v>
-      </c>
-      <c r="G10" t="s">
-        <v>52</v>
-      </c>
-      <c r="H10">
-        <v>0.8</v>
-      </c>
-      <c r="I10" t="s">
-        <v>52</v>
-      </c>
-      <c r="J10">
-        <v>0.8</v>
-      </c>
-      <c r="K10" t="s">
-        <v>52</v>
+        <v/>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="str">
         <f>IF(ISBLANK(interventions!A11),"",interventions!A11)</f>
-        <v>prison_counter_all</v>
-      </c>
-      <c r="D11">
-        <v>0.8</v>
-      </c>
-      <c r="E11" t="s">
-        <v>52</v>
-      </c>
-      <c r="F11">
-        <v>0.8</v>
-      </c>
-      <c r="G11" t="s">
-        <v>52</v>
-      </c>
-      <c r="H11">
-        <v>0.8</v>
-      </c>
-      <c r="I11" t="s">
-        <v>52</v>
-      </c>
+        <v/>
+      </c>
+      <c r="H11" s="5"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="str">
@@ -3943,7 +3707,6 @@
         <f>IF(ISBLANK(interventions!A17),"",interventions!A17)</f>
         <v/>
       </c>
-      <c r="H17" s="5"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="str">
@@ -3974,26 +3737,26 @@
         <f>IF(ISBLANK(interventions!A22),"",interventions!A22)</f>
         <v/>
       </c>
+      <c r="H22" s="5"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="str">
         <f>IF(ISBLANK(interventions!A23),"",interventions!A23)</f>
         <v/>
       </c>
+      <c r="H23" s="5"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="str">
         <f>IF(ISBLANK(interventions!A24),"",interventions!A24)</f>
         <v/>
       </c>
-      <c r="H24" s="5"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="str">
         <f>IF(ISBLANK(interventions!A25),"",interventions!A25)</f>
         <v/>
       </c>
-      <c r="H25" s="5"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="str">
@@ -4115,21 +3878,9 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A46" s="4" t="str">
-        <f>IF(ISBLANK(interventions!A46),"",interventions!A46)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A47" s="4" t="str">
-        <f>IF(ISBLANK(interventions!A47),"",interventions!A47)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M47 C2:C47 K2:K47 I2:I47 E2:E47 G2:G47" xr:uid="{9A136EE2-9E44-426F-8888-910675484DBA}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G45 E2:E45 I2:I45 K2:K45 C2:C45 M2:M45" xr:uid="{9A136EE2-9E44-426F-8888-910675484DBA}">
       <formula1>"RR, OR, PROB"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4141,7 +3892,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C010CA95-9913-4E01-BBC8-E12EAEB492A2}">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.81640625" bestFit="1" customWidth="1"/>
@@ -4244,67 +3995,69 @@
       <c r="F5" s="21"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="B6" s="29" t="s">
-        <v>92</v>
-      </c>
-      <c r="C6" s="29" t="s">
-        <v>63</v>
-      </c>
-      <c r="D6" s="29">
+      <c r="A6" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="21">
         <v>2027</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="21">
+        <v>2050</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7">
         <v>2028</v>
       </c>
-      <c r="F6" s="29"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="26" t="s">
-        <v>91</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="D7" s="21">
-        <v>2027</v>
-      </c>
-      <c r="E7" s="21">
+      <c r="E7">
         <v>2050</v>
       </c>
-      <c r="F7" s="21"/>
+      <c r="F7" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="25" t="s">
-        <v>73</v>
+      <c r="A8" s="24" t="s">
+        <v>74</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D8" s="21">
         <v>2027</v>
       </c>
       <c r="E8" s="21">
-        <v>2050</v>
-      </c>
-      <c r="F8" s="21" t="s">
-        <v>70</v>
-      </c>
+        <v>2028</v>
+      </c>
+      <c r="F8" s="21"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="16" t="s">
-        <v>74</v>
+      <c r="A9" s="17" t="s">
+        <v>75</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C9" t="s">
         <v>38</v>
@@ -4316,172 +4069,168 @@
         <v>2050</v>
       </c>
       <c r="F9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="B10" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="C10" s="21" t="s">
+      <c r="A10" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="B10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="21">
+      <c r="D10">
         <v>2027</v>
       </c>
-      <c r="E10" s="21">
+      <c r="E10">
         <v>2028</v>
       </c>
-      <c r="F10" s="21"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="B11" t="s">
-        <v>87</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B11" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="21">
+        <v>2027</v>
+      </c>
+      <c r="E11" s="21">
+        <v>2050</v>
+      </c>
+      <c r="F11" s="21"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" t="s">
         <v>38</v>
       </c>
-      <c r="D11">
+      <c r="D12">
         <v>2028</v>
       </c>
-      <c r="E11">
+      <c r="E12">
         <v>2050</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F12" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="B12" t="s">
-        <v>87</v>
-      </c>
-      <c r="C12" t="s">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" t="s">
         <v>39</v>
       </c>
-      <c r="D12">
+      <c r="D13">
         <v>2027</v>
       </c>
-      <c r="E12">
+      <c r="E13">
         <v>2028</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" s="21">
-        <v>2027</v>
-      </c>
-      <c r="E13" s="21">
-        <v>2050</v>
-      </c>
-      <c r="F13" s="21"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="18" t="s">
         <v>76</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D14">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="E14">
         <v>2050</v>
       </c>
-      <c r="F14" t="s">
-        <v>72</v>
-      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="B15" t="s">
-        <v>93</v>
-      </c>
-      <c r="C15" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15">
+      <c r="B15" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="21">
         <v>2027</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="21">
+        <v>2050</v>
+      </c>
+      <c r="F15" s="21"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16">
         <v>2028</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="B16" t="s">
-        <v>93</v>
-      </c>
-      <c r="C16" t="s">
-        <v>40</v>
-      </c>
-      <c r="D16">
-        <v>2027</v>
       </c>
       <c r="E16">
         <v>2050</v>
       </c>
+      <c r="F16" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="B17" s="21" t="s">
-        <v>93</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" s="21">
+      <c r="A17" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" t="s">
+        <v>86</v>
+      </c>
+      <c r="C17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17">
         <v>2027</v>
       </c>
-      <c r="E17" s="21">
-        <v>2050</v>
-      </c>
-      <c r="F17" s="21"/>
+      <c r="E17">
+        <v>2028</v>
+      </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="19" t="s">
         <v>77</v>
       </c>
       <c r="B18" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C18" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D18">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="E18">
         <v>2050</v>
-      </c>
-      <c r="F18" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -4489,125 +4238,36 @@
         <v>77</v>
       </c>
       <c r="B19" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D19">
         <v>2027</v>
       </c>
       <c r="E19">
-        <v>2028</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B20" t="s">
-        <v>94</v>
-      </c>
-      <c r="C20" t="s">
-        <v>40</v>
-      </c>
-      <c r="D20">
+      <c r="B20" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" s="21">
         <v>2027</v>
       </c>
-      <c r="E20">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="B21" t="s">
-        <v>94</v>
-      </c>
-      <c r="C21" t="s">
-        <v>37</v>
-      </c>
-      <c r="D21">
-        <v>2027</v>
-      </c>
-      <c r="E21">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="B22" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="C22" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="D22" s="21">
-        <v>2027</v>
-      </c>
-      <c r="E22" s="21">
-        <f>D22+5</f>
+      <c r="E20" s="21">
+        <f>D20+5</f>
         <v>2032</v>
       </c>
-      <c r="F22" s="21"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="B23" t="s">
-        <v>90</v>
-      </c>
-      <c r="C23" t="s">
-        <v>38</v>
-      </c>
-      <c r="D23">
-        <v>2028</v>
-      </c>
-      <c r="E23">
-        <v>2050</v>
-      </c>
-      <c r="F23" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="B24" t="s">
-        <v>90</v>
-      </c>
-      <c r="C24" t="s">
-        <v>39</v>
-      </c>
-      <c r="D24">
-        <v>2027</v>
-      </c>
-      <c r="E24">
-        <v>2028</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="B25" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="C25" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D25" s="21">
-        <v>2027</v>
-      </c>
-      <c r="E25" s="21">
-        <v>2050</v>
-      </c>
-      <c r="F25" s="21"/>
+      <c r="F20" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4617,6 +4277,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="460e4ad2-c64b-4f67-8552-094351f252e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010042DC9346A4EFF44B9278E035670E998A" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b6002ac4d6852791cc52372fb08f1f93">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="460e4ad2-c64b-4f67-8552-094351f252e3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d81800e77b8320248f69566da91fdce8" ns2:_="">
     <xsd:import namespace="460e4ad2-c64b-4f67-8552-094351f252e3"/>
@@ -4788,26 +4467,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA2D8656-6848-4E43-8697-69A82BA725E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="460e4ad2-c64b-4f67-8552-094351f252e3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="460e4ad2-c64b-4f67-8552-094351f252e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3882B21-9C06-4A25-BA73-35DB35426A28}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090DCA50-A1C8-4B02-A520-4AE25ED4C282}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4823,28 +4507,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3882B21-9C06-4A25-BA73-35DB35426A28}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA2D8656-6848-4E43-8697-69A82BA725E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="460e4ad2-c64b-4f67-8552-094351f252e3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/progbook_inputs.xlsx
+++ b/data/progbook_inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farah.houdroge\Documents\GitHub\hcv-vaccine\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3388EFF-6C17-458E-8601-94BC18157DB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B50FD642-71D4-4058-B2EF-DD993AED39E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E2E90E70-2F54-4097-8786-78C8F6F97317}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E2E90E70-2F54-4097-8786-78C8F6F97317}"/>
   </bookViews>
   <sheets>
     <sheet name="interventions" sheetId="7" r:id="rId1"/>
@@ -482,7 +482,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="87">
   <si>
     <t>code</t>
   </si>
@@ -1626,8 +1626,12 @@
       <c r="I4" s="11"/>
       <c r="J4" s="11"/>
       <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
+      <c r="L4" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="N4" s="11" t="s">
         <v>15</v>
       </c>
@@ -1722,8 +1726,12 @@
       <c r="I8" s="11"/>
       <c r="J8" s="11"/>
       <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
+      <c r="L8" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="N8" s="11" t="s">
         <v>15</v>
       </c>
@@ -2428,12 +2436,12 @@
       <c r="M45" s="11"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:M45">
+  <conditionalFormatting sqref="B2:M3 B9:M45 B4:K8">
     <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"y"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N4:O9">
+  <conditionalFormatting sqref="N4:O9 L4:M8">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"y"</formula>
     </cfRule>
@@ -4277,25 +4285,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="460e4ad2-c64b-4f67-8552-094351f252e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010042DC9346A4EFF44B9278E035670E998A" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b6002ac4d6852791cc52372fb08f1f93">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="460e4ad2-c64b-4f67-8552-094351f252e3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d81800e77b8320248f69566da91fdce8" ns2:_="">
     <xsd:import namespace="460e4ad2-c64b-4f67-8552-094351f252e3"/>
@@ -4467,31 +4456,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA2D8656-6848-4E43-8697-69A82BA725E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="460e4ad2-c64b-4f67-8552-094351f252e3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3882B21-9C06-4A25-BA73-35DB35426A28}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="460e4ad2-c64b-4f67-8552-094351f252e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090DCA50-A1C8-4B02-A520-4AE25ED4C282}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4507,4 +4491,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3882B21-9C06-4A25-BA73-35DB35426A28}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA2D8656-6848-4E43-8697-69A82BA725E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="460e4ad2-c64b-4f67-8552-094351f252e3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>